--- a/paper/Tables/Balance2.xlsx
+++ b/paper/Tables/Balance2.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,13 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93E50A3-CB92-48DB-9521-3EB870AABE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25260" yWindow="-4845" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25260" yWindow="-4845" windowWidth="21600" windowHeight="11175"/>
   </bookViews>
   <sheets>
     <sheet name="Balance" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="97">
   <si>
     <t>Phase 1</t>
   </si>
@@ -108,6 +108,114 @@
   </si>
   <si>
     <t>Tenure at firm (years)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t/>
@@ -296,10 +404,10 @@
       <left/>
       <right/>
       <top style="double">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -329,55 +437,55 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -697,10 +805,10 @@
   <dimension ref="A3:W17"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="19" t="s">
         <v>0</v>
@@ -718,7 +826,7 @@
       <c r="I3" s="19"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:23" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" ht="15.5" thickTop="true" thickBot="true" x14ac:dyDescent="0.4">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
         <v>3</v>
@@ -748,7 +856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="15" thickTop="true" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
@@ -795,37 +903,37 @@
         <v>0.10486891385767791</v>
       </c>
       <c r="N5">
-        <v>0.64</v>
+        <v>0.64000000000000001</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>9.7178683385579931E-2</v>
+        <v>0.097178683385579931</v>
       </c>
       <c r="Q5">
-        <v>7.2916666666666671E-2</v>
+        <v>0.072916666666666671</v>
       </c>
       <c r="R5">
-        <v>0.2</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="S5" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="T5">
         <v>0.10666666666666667</v>
       </c>
       <c r="U5">
-        <v>8.1159420289855067E-2</v>
+        <v>0.081159420289855067</v>
       </c>
       <c r="V5">
-        <v>0.09</v>
+        <v>0.089999999999999997</v>
       </c>
       <c r="W5" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>24</v>
       </c>
@@ -875,7 +983,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="P6">
         <v>4.9656503210077894</v>
@@ -884,10 +992,10 @@
         <v>4.1054366380291567</v>
       </c>
       <c r="R6">
-        <v>7.0000000000000007E-2</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="T6">
         <v>4.9080439460673579</v>
@@ -896,13 +1004,13 @@
         <v>4.2218619497420571</v>
       </c>
       <c r="V6">
-        <v>0.04</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="W6" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
@@ -952,34 +1060,34 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="P7">
-        <v>5.6426332288401257E-2</v>
+        <v>0.056426332288401257</v>
       </c>
       <c r="Q7">
-        <v>6.1197916666666664E-2</v>
+        <v>0.061197916666666664</v>
       </c>
       <c r="R7">
-        <v>0.76</v>
+        <v>0.76000000000000001</v>
       </c>
       <c r="S7" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="T7">
-        <v>0.08</v>
+        <v>0.080000000000000002</v>
       </c>
       <c r="U7">
-        <v>7.7285579641847318E-2</v>
+        <v>0.077285579641847318</v>
       </c>
       <c r="V7">
-        <v>0.84</v>
+        <v>0.83999999999999997</v>
       </c>
       <c r="W7" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1029,7 +1137,7 @@
         <v>0.31</v>
       </c>
       <c r="O8" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="P8">
         <v>0.80877742946708464</v>
@@ -1038,10 +1146,10 @@
         <v>0.79269882659713164</v>
       </c>
       <c r="R8">
-        <v>0.54</v>
+        <v>0.54000000000000004</v>
       </c>
       <c r="S8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="T8">
         <v>0.81499999999999995</v>
@@ -1053,10 +1161,10 @@
         <v>0.75</v>
       </c>
       <c r="W8" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1103,10 +1211,10 @@
         <v>624.23694242368276</v>
       </c>
       <c r="N9">
-        <v>0.03</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="O9" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="P9">
         <v>617.35028779076754</v>
@@ -1115,10 +1223,10 @@
         <v>600.51842392981052</v>
       </c>
       <c r="R9">
-        <v>0.85</v>
+        <v>0.84999999999999998</v>
       </c>
       <c r="S9" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="T9">
         <v>740.05307764412794</v>
@@ -1127,13 +1235,13 @@
         <v>606.56883165424154</v>
       </c>
       <c r="V9">
-        <v>0.06</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="W9" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
@@ -1180,10 +1288,10 @@
         <v>0.8539325842696629</v>
       </c>
       <c r="N10">
-        <v>0.06</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="O10" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="P10">
         <v>0.79623824451410663</v>
@@ -1195,7 +1303,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="T10">
         <v>0.79500000000000004</v>
@@ -1204,13 +1312,13 @@
         <v>0.79903381642512072</v>
       </c>
       <c r="V10">
-        <v>0.85</v>
+        <v>0.84999999999999998</v>
       </c>
       <c r="W10" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>16</v>
       </c>
@@ -1257,10 +1365,10 @@
         <v>71391.91146874243</v>
       </c>
       <c r="N11">
-        <v>0.03</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="O11" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="P11">
         <v>63189.713784340405</v>
@@ -1272,7 +1380,7 @@
         <v>0.5</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="T11">
         <v>78992.763075258932</v>
@@ -1281,13 +1389,13 @@
         <v>69519.730985347749</v>
       </c>
       <c r="V11">
-        <v>0.18</v>
+        <v>0.17999999999999999</v>
       </c>
       <c r="W11" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>11</v>
       </c>
@@ -1334,10 +1442,10 @@
         <v>0.19682539682539682</v>
       </c>
       <c r="N12">
-        <v>0.91</v>
+        <v>0.91000000000000003</v>
       </c>
       <c r="O12" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="P12">
         <v>0.15548780487804878</v>
@@ -1349,7 +1457,7 @@
         <v>0.13</v>
       </c>
       <c r="S12" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="T12">
         <v>0.17411402157164868</v>
@@ -1358,13 +1466,13 @@
         <v>0.19390581717451524</v>
       </c>
       <c r="V12">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="W12" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
@@ -1411,10 +1519,10 @@
         <v>0.83174603174603179</v>
       </c>
       <c r="N13">
-        <v>0.59</v>
+        <v>0.58999999999999997</v>
       </c>
       <c r="O13" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="P13">
         <v>0.91768292682926833</v>
@@ -1426,7 +1534,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="S13" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="T13">
         <v>0.88289676425269648</v>
@@ -1435,13 +1543,13 @@
         <v>0.87257617728531855</v>
       </c>
       <c r="V13">
-        <v>0.52</v>
+        <v>0.52000000000000002</v>
       </c>
       <c r="W13" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
@@ -1482,43 +1590,43 @@
         <v>0.8</v>
       </c>
       <c r="L14">
-        <v>3.4267912772585667E-2</v>
+        <v>0.034267912772585667</v>
       </c>
       <c r="M14">
-        <v>1.9047619047619049E-2</v>
+        <v>0.019047619047619049</v>
       </c>
       <c r="N14">
-        <v>0.23</v>
+        <v>0.23000000000000001</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="P14">
-        <v>1.2195121951219513E-2</v>
+        <v>0.012195121951219513</v>
       </c>
       <c r="Q14">
-        <v>2.2135416666666668E-2</v>
+        <v>0.022135416666666668</v>
       </c>
       <c r="R14">
         <v>0.22</v>
       </c>
       <c r="S14" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="T14">
-        <v>2.3112480739599383E-2</v>
+        <v>0.023112480739599383</v>
       </c>
       <c r="U14">
-        <v>2.1237303785780239E-2</v>
+        <v>0.021237303785780239</v>
       </c>
       <c r="V14">
-        <v>0.8</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="W14" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
@@ -1565,10 +1673,10 @@
         <v>0.76190476190476186</v>
       </c>
       <c r="N15">
-        <v>0.49</v>
+        <v>0.48999999999999999</v>
       </c>
       <c r="O15" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="P15">
         <v>0.78963414634146345</v>
@@ -1580,7 +1688,7 @@
         <v>0.83000000000000007</v>
       </c>
       <c r="S15" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="T15">
         <v>0.76425269645608629</v>
@@ -1589,13 +1697,13 @@
         <v>0.77746999076638967</v>
       </c>
       <c r="V15">
-        <v>0.53</v>
+        <v>0.53000000000000003</v>
       </c>
       <c r="W15" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="15" thickTop="true" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>10</v>
       </c>
@@ -1645,7 +1753,7 @@
         <v>0.5828090663114267</v>
       </c>
       <c r="O16" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="P16">
         <v>328</v>
@@ -1657,7 +1765,7 @@
         <v>0.19626292409435719</v>
       </c>
       <c r="S16" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="T16">
         <v>649</v>
@@ -1669,10 +1777,10 @@
         <v>0.1064411732967797</v>
       </c>
       <c r="W16" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" x14ac:dyDescent="0.35">
       <c r="B17" s="12"/>
       <c r="E17" s="12"/>
     </row>
@@ -1691,11 +1799,11 @@
   <dimension ref="G5:L9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" bestFit="true" customWidth="true"/>
     <col min="8" max="12" width="8.7265625" style="14"/>
   </cols>
   <sheetData>
-    <row r="5" spans="7:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="G5" s="15" t="s">
         <v>17</v>
       </c>
@@ -1715,7 +1823,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="7:12" x14ac:dyDescent="0.35">
+    <row r="6" x14ac:dyDescent="0.35">
       <c r="G6" t="s">
         <v>15</v>
       </c>
@@ -1735,7 +1843,7 @@
         <v>16080.02</v>
       </c>
     </row>
-    <row r="7" spans="7:12" x14ac:dyDescent="0.35">
+    <row r="7" x14ac:dyDescent="0.35">
       <c r="G7" t="s">
         <v>16</v>
       </c>
@@ -1755,7 +1863,7 @@
         <v>1632039</v>
       </c>
     </row>
-    <row r="8" spans="7:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" ht="15" thickBot="true" x14ac:dyDescent="0.4">
       <c r="G8" s="17" t="s">
         <v>23</v>
       </c>
@@ -1775,7 +1883,7 @@
         <v>5.1123289999999999</v>
       </c>
     </row>
-    <row r="9" spans="7:12" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="9" ht="15" thickTop="true" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
